--- a/sales_order_forms/006_maintenance_spray_lubricant_order_form--sales_order_forms.xlsx
+++ b/sales_order_forms/006_maintenance_spray_lubricant_order_form--sales_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -784,8 +784,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -813,12 +813,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'lubri_1',_'label':_'lubri_1'}</t>
+          <t>lubri_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Lubri 1', 'label': 'Lubri 1'}</t>
+          <t>Lubri 1</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'lubri_2',_'label':_'lubri_2'}</t>
+          <t>lubri_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Lubri 2', 'label': 'Lubri 2'}</t>
+          <t>Lubri 2</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'1%',_'label':_'1%'}</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': '1%', 'label': '1%'}</t>
+          <t>1%</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'2%',_'label':_'2%'}</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': '2%', 'label': '2%'}</t>
+          <t>2%</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'5%',_'label':_'5%'}</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': '5%', 'label': '5%'}</t>
+          <t>5%</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'chatjimmy',_'label':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'chatjimmy', 'label': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'in_progress',_'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'In Progress', 'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'completed',_'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Completed', 'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
